--- a/ig/DM-37/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
